--- a/out/07_Ops/SNX-OPS-FRM-09 SLA Performance Monitoring Report (Rev00 DRAFT).xlsx
+++ b/out/07_Ops/SNX-OPS-FRM-09 SLA Performance Monitoring Report (Rev00 DRAFT).xlsx
@@ -15,8 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Laporan Bulanan" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Daftar'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Parameter SLA'!$A$4:$I$46</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Parameter SLA'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Downtime Log'!$A$4:$K$206</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Downtime Log'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Laporan Bulanan'!$7:$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -179,7 +183,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -381,6 +385,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -767,8 +804,15 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="37">
-      <c r="A4" s="40" t="inlineStr">
+    <row r="3" s="37">
+      <c r="A3" s="68" t="n"/>
+      <c r="B3" s="68" t="n"/>
+      <c r="C3" s="68" t="n"/>
+      <c r="D3" s="68" t="n"/>
+      <c r="E3" s="68" t="n"/>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="37">
+      <c r="A4" s="69" t="inlineStr">
         <is>
           <t>Nomor dokumen</t>
         </is>
@@ -778,9 +822,12 @@
           <t>SNX-OPS-FRM-09</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="37">
-      <c r="A5" s="40" t="inlineStr">
+      <c r="C4" s="68" t="n"/>
+      <c r="D4" s="68" t="n"/>
+      <c r="E4" s="68" t="n"/>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="37">
+      <c r="A5" s="69" t="inlineStr">
         <is>
           <t>Judul</t>
         </is>
@@ -790,9 +837,12 @@
           <t>SLA Performance Monitoring Report</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="37">
-      <c r="A6" s="40" t="inlineStr">
+      <c r="C5" s="68" t="n"/>
+      <c r="D5" s="68" t="n"/>
+      <c r="E5" s="68" t="n"/>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" s="37">
+      <c r="A6" s="69" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
@@ -802,9 +852,12 @@
           <t>00 (Draft)</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="37">
-      <c r="A7" s="40" t="inlineStr">
+      <c r="C6" s="68" t="n"/>
+      <c r="D6" s="68" t="n"/>
+      <c r="E6" s="68" t="n"/>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" s="37">
+      <c r="A7" s="69" t="inlineStr">
         <is>
           <t>Tanggal draft</t>
         </is>
@@ -814,9 +867,12 @@
           <t>13 Oktober 2026</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="37">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="C7" s="68" t="n"/>
+      <c r="D7" s="68" t="n"/>
+      <c r="E7" s="68" t="n"/>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" s="37">
+      <c r="A8" s="69" t="inlineStr">
         <is>
           <t>Tanggal efektif</t>
         </is>
@@ -826,9 +882,12 @@
           <t>Ditetapkan saat pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="37">
-      <c r="A9" s="40" t="inlineStr">
+      <c r="C8" s="68" t="n"/>
+      <c r="D8" s="68" t="n"/>
+      <c r="E8" s="68" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" s="37">
+      <c r="A9" s="69" t="inlineStr">
         <is>
           <t>Klasifikasi</t>
         </is>
@@ -838,9 +897,12 @@
           <t>RESTRICTED (Internal)</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="37">
-      <c r="A10" s="40" t="inlineStr">
+      <c r="C9" s="68" t="n"/>
+      <c r="D9" s="68" t="n"/>
+      <c r="E9" s="68" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="37">
+      <c r="A10" s="69" t="inlineStr">
         <is>
           <t>Pemilik dokumen</t>
         </is>
@@ -850,9 +912,12 @@
           <t>Service Delivery Manager</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="37">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="C10" s="68" t="n"/>
+      <c r="D10" s="68" t="n"/>
+      <c r="E10" s="68" t="n"/>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" s="37">
+      <c r="A11" s="69" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
@@ -862,9 +927,12 @@
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="37">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="C11" s="68" t="n"/>
+      <c r="D11" s="68" t="n"/>
+      <c r="E11" s="68" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" s="37">
+      <c r="A12" s="69" t="inlineStr">
         <is>
           <t>Acuan ISO 9001:2015</t>
         </is>
@@ -874,9 +942,12 @@
           <t>Klausul 9.1.1, 9.1.2, 9.1.3</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="37">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="C12" s="68" t="n"/>
+      <c r="D12" s="68" t="n"/>
+      <c r="E12" s="68" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" s="37">
+      <c r="A13" s="69" t="inlineStr">
         <is>
           <t>Acuan ISO/IEC 27001:2022</t>
         </is>
@@ -886,9 +957,12 @@
           <t>Kontrol Annex A 8.16</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="37">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="C13" s="68" t="n"/>
+      <c r="D13" s="68" t="n"/>
+      <c r="E13" s="68" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" s="37">
+      <c r="A14" s="69" t="inlineStr">
         <is>
           <t>Masa simpan record</t>
         </is>
@@ -898,9 +972,12 @@
           <t>3 tahun</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="23.85" customHeight="1" s="37">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="C14" s="68" t="n"/>
+      <c r="D14" s="68" t="n"/>
+      <c r="E14" s="68" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1" s="37">
+      <c r="A15" s="69" t="inlineStr">
         <is>
           <t>Tujuan</t>
         </is>
@@ -910,64 +987,90 @@
           <t>Parameter SLA per pelanggan, log downtime, dan laporan availability bulanan sesuai SNX-OPS-SOP-05.</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="37">
-      <c r="A17" s="42" t="inlineStr">
+      <c r="C15" s="68" t="n"/>
+      <c r="D15" s="68" t="n"/>
+      <c r="E15" s="68" t="n"/>
+    </row>
+    <row r="16" s="37">
+      <c r="A16" s="68" t="n"/>
+      <c r="B16" s="68" t="n"/>
+      <c r="C16" s="68" t="n"/>
+      <c r="D16" s="68" t="n"/>
+      <c r="E16" s="68" t="n"/>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="37">
+      <c r="A17" s="70" t="inlineStr">
         <is>
           <t>Cara pakai</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="37">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="B17" s="68" t="n"/>
+      <c r="C17" s="68" t="n"/>
+      <c r="D17" s="68" t="n"/>
+      <c r="E17" s="68" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1" s="37">
+      <c r="A18" s="44" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
       <c r="B18" s="44" t="inlineStr">
         <is>
-          <t>Daftarkan tiap layanan ber-SLA di sheet Parameter SLA saat onboarding.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="23.85" customHeight="1" s="37">
-      <c r="A19" s="43" t="inlineStr">
+          <t>Daftarkan setiap layanan ber-SLA di sheet Parameter SLA saat onboarding.</t>
+        </is>
+      </c>
+      <c r="C18" s="68" t="n"/>
+      <c r="D18" s="68" t="n"/>
+      <c r="E18" s="68" t="n"/>
+    </row>
+    <row r="19" ht="43.5" customHeight="1" s="37">
+      <c r="A19" s="44" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
       <c r="B19" s="44" t="inlineStr">
         <is>
-          <t>Catat setiap downtime di Downtime Log; kolom Dihitung = Tidak hanya bila ada bukti notifikasi maintenance atau pengecualian kontrak.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="23.85" customHeight="1" s="37">
-      <c r="A20" s="43" t="inlineStr">
+          <t>Catat setiap downtime di Downtime Log. Isi kolom Dihitung dengan "Tidak" hanya jika ada bukti notifikasi maintenance atau pengecualian kontrak.</t>
+        </is>
+      </c>
+      <c r="C19" s="68" t="n"/>
+      <c r="D19" s="68" t="n"/>
+      <c r="E19" s="68" t="n"/>
+    </row>
+    <row r="20" ht="43.5" customHeight="1" s="37">
+      <c r="A20" s="44" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
       <c r="B20" s="44" t="inlineStr">
         <is>
-          <t>Pilih bulan laporan di sheet Laporan Bulanan sel B3; availability, status, dan sisa anggaran downtime dihitung otomatis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="37">
-      <c r="A21" s="43" t="inlineStr">
+          <t>Pilih bulan laporan di sel B3 sheet Laporan Bulanan. Availability, status, dan sisa anggaran downtime terisi otomatis.</t>
+        </is>
+      </c>
+      <c r="C20" s="68" t="n"/>
+      <c r="D20" s="68" t="n"/>
+      <c r="E20" s="68" t="n"/>
+    </row>
+    <row r="21" ht="16.5" customHeight="1" s="37">
+      <c r="A21" s="44" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
       <c r="B21" s="44" t="inlineStr">
         <is>
-          <t>Isi data respon tiket dari ringkasan SNX-OPS-FRM-08.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="37">
-      <c r="A22" s="43" t="inlineStr">
+          <t>Isi data respons ticket dari ringkasan SNX-OPS-FRM-08.</t>
+        </is>
+      </c>
+      <c r="C21" s="68" t="n"/>
+      <c r="D21" s="68" t="n"/>
+      <c r="E21" s="68" t="n"/>
+    </row>
+    <row r="22" ht="16.5" customHeight="1" s="37">
+      <c r="A22" s="44" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
@@ -977,73 +1080,107 @@
           <t>Kirim laporan ke pelanggan paling lambat hari kerja ke-5.</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="37">
-      <c r="A24" s="42" t="inlineStr">
+      <c r="C22" s="68" t="n"/>
+      <c r="D22" s="68" t="n"/>
+      <c r="E22" s="68" t="n"/>
+    </row>
+    <row r="23" s="37">
+      <c r="A23" s="68" t="n"/>
+      <c r="B23" s="68" t="n"/>
+      <c r="C23" s="68" t="n"/>
+      <c r="D23" s="68" t="n"/>
+      <c r="E23" s="68" t="n"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="37">
+      <c r="A24" s="70" t="inlineStr">
         <is>
           <t>Legenda warna</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="37">
-      <c r="A25" s="45" t="n"/>
-      <c r="B25" s="43" t="inlineStr">
+      <c r="B24" s="68" t="n"/>
+      <c r="C24" s="68" t="n"/>
+      <c r="D24" s="68" t="n"/>
+      <c r="E24" s="68" t="n"/>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" s="37">
+      <c r="A25" s="71" t="n"/>
+      <c r="B25" s="44" t="inlineStr">
         <is>
           <t>Sel input: diisi pengguna</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="37">
-      <c r="A26" s="46" t="n"/>
-      <c r="B26" s="43" t="inlineStr">
+      <c r="C25" s="68" t="n"/>
+      <c r="D25" s="68" t="n"/>
+      <c r="E25" s="68" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1" s="37">
+      <c r="A26" s="72" t="n"/>
+      <c r="B26" s="44" t="inlineStr">
         <is>
           <t>Biru muda: warna baris contoh, sudah dikosongkan dan tidak dipakai</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="37">
-      <c r="A27" s="47" t="n"/>
-      <c r="B27" s="43" t="inlineStr">
+      <c r="C26" s="68" t="n"/>
+      <c r="D26" s="68" t="n"/>
+      <c r="E26" s="68" t="n"/>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" s="37">
+      <c r="A27" s="73" t="n"/>
+      <c r="B27" s="44" t="inlineStr">
         <is>
           <t>Sel rumus: jangan diubah</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="37">
-      <c r="A29" s="42" t="inlineStr">
+      <c r="C27" s="68" t="n"/>
+      <c r="D27" s="68" t="n"/>
+      <c r="E27" s="68" t="n"/>
+    </row>
+    <row r="28" s="37">
+      <c r="A28" s="68" t="n"/>
+      <c r="B28" s="68" t="n"/>
+      <c r="C28" s="68" t="n"/>
+      <c r="D28" s="68" t="n"/>
+      <c r="E28" s="68" t="n"/>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" s="37">
+      <c r="A29" s="70" t="inlineStr">
         <is>
           <t>Riwayat revisi</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="37">
-      <c r="A30" s="48" t="inlineStr">
+      <c r="B29" s="68" t="n"/>
+      <c r="C29" s="68" t="n"/>
+      <c r="D29" s="68" t="n"/>
+      <c r="E29" s="68" t="n"/>
+    </row>
+    <row r="30" ht="16.5" customHeight="1" s="37">
+      <c r="A30" s="52" t="inlineStr">
         <is>
           <t>Revisi</t>
         </is>
       </c>
-      <c r="B30" s="48" t="inlineStr">
+      <c r="B30" s="52" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
-      <c r="C30" s="48" t="inlineStr">
+      <c r="C30" s="52" t="inlineStr">
         <is>
           <t>Uraian perubahan</t>
         </is>
       </c>
-      <c r="D30" s="48" t="inlineStr">
+      <c r="D30" s="52" t="inlineStr">
         <is>
           <t>Disusun</t>
         </is>
       </c>
-      <c r="E30" s="48" t="inlineStr">
+      <c r="E30" s="52" t="inlineStr">
         <is>
           <t>Disetujui</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="23.85" customHeight="1" s="37">
+    <row r="31" ht="30" customHeight="1" s="37">
       <c r="A31" s="41" t="inlineStr">
         <is>
           <t>00</t>
@@ -1077,76 +1214,91 @@
       <c r="D32" s="41" t="n"/>
       <c r="E32" s="41" t="n"/>
     </row>
-    <row r="34" ht="15" customHeight="1" s="37">
-      <c r="A34" s="42" t="inlineStr">
+    <row r="33" s="37">
+      <c r="A33" s="68" t="n"/>
+      <c r="B33" s="68" t="n"/>
+      <c r="C33" s="68" t="n"/>
+      <c r="D33" s="68" t="n"/>
+      <c r="E33" s="68" t="n"/>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="37">
+      <c r="A34" s="70" t="inlineStr">
         <is>
           <t>Pengesahan</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="37">
-      <c r="A35" s="48" t="inlineStr">
+      <c r="B34" s="68" t="n"/>
+      <c r="C34" s="68" t="n"/>
+      <c r="D34" s="68" t="n"/>
+      <c r="E34" s="68" t="n"/>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" s="37">
+      <c r="A35" s="52" t="inlineStr">
         <is>
           <t>Peran</t>
         </is>
       </c>
-      <c r="B35" s="48" t="inlineStr">
+      <c r="B35" s="52" t="inlineStr">
         <is>
           <t>Nama dan jabatan</t>
         </is>
       </c>
-      <c r="C35" s="48" t="inlineStr">
+      <c r="C35" s="52" t="inlineStr">
         <is>
           <t>Tanda tangan</t>
         </is>
       </c>
-      <c r="D35" s="48" t="inlineStr">
+      <c r="D35" s="52" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
+      <c r="E35" s="68" t="n"/>
     </row>
     <row r="36" ht="27.75" customHeight="1" s="37">
-      <c r="A36" s="49" t="inlineStr">
+      <c r="A36" s="41" t="inlineStr">
         <is>
           <t>Disusun oleh</t>
         </is>
       </c>
-      <c r="B36" s="49" t="inlineStr">
+      <c r="B36" s="41" t="inlineStr">
         <is>
           <t>Erik Dwi Yanto / Technical/Operation Engineer L1</t>
         </is>
       </c>
-      <c r="C36" s="49" t="n"/>
-      <c r="D36" s="49" t="n"/>
+      <c r="C36" s="41" t="n"/>
+      <c r="D36" s="41" t="n"/>
+      <c r="E36" s="68" t="n"/>
     </row>
     <row r="37" ht="27.75" customHeight="1" s="37">
-      <c r="A37" s="49" t="inlineStr">
+      <c r="A37" s="41" t="inlineStr">
         <is>
           <t>Diperiksa oleh</t>
         </is>
       </c>
-      <c r="B37" s="49" t="inlineStr">
+      <c r="B37" s="41" t="inlineStr">
         <is>
           <t>Fani Fatullah / VP Tech Operation and Services</t>
         </is>
       </c>
-      <c r="C37" s="49" t="n"/>
-      <c r="D37" s="49" t="n"/>
+      <c r="C37" s="41" t="n"/>
+      <c r="D37" s="41" t="n"/>
+      <c r="E37" s="68" t="n"/>
     </row>
     <row r="38" ht="27.75" customHeight="1" s="37">
-      <c r="A38" s="49" t="inlineStr">
+      <c r="A38" s="41" t="inlineStr">
         <is>
           <t>Disetujui oleh</t>
         </is>
       </c>
-      <c r="B38" s="49" t="inlineStr">
+      <c r="B38" s="41" t="inlineStr">
         <is>
           <t>Samuel Kristanto Utomo / President Director</t>
         </is>
       </c>
-      <c r="C38" s="49" t="n"/>
-      <c r="D38" s="49" t="n"/>
+      <c r="C38" s="41" t="n"/>
+      <c r="D38" s="41" t="n"/>
+      <c r="E38" s="68" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -1190,7 +1342,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
@@ -1199,72 +1351,77 @@
     <col width="26" customWidth="1" style="36" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="37">
-      <c r="A1" s="51" t="inlineStr">
+    <row r="1" ht="16.5" customHeight="1" s="37">
+      <c r="A1" s="74" t="inlineStr">
         <is>
           <t>Dihitung</t>
         </is>
       </c>
-      <c r="B1" s="51" t="inlineStr">
+      <c r="B1" s="74" t="inlineStr">
         <is>
           <t>Penyebab</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="37">
-      <c r="A2" s="43" t="inlineStr">
+    <row r="2" ht="16.5" customHeight="1" s="37">
+      <c r="A2" s="75" t="inlineStr">
         <is>
           <t>Ya</t>
         </is>
       </c>
-      <c r="B2" s="43" t="inlineStr">
+      <c r="B2" s="75" t="inlineStr">
         <is>
           <t>Platform SINUX</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="37">
-      <c r="A3" s="43" t="inlineStr">
+    <row r="3" ht="16.5" customHeight="1" s="37">
+      <c r="A3" s="75" t="inlineStr">
         <is>
           <t>Tidak</t>
         </is>
       </c>
-      <c r="B3" s="43" t="inlineStr">
+      <c r="B3" s="75" t="inlineStr">
         <is>
           <t>Upstream atau supplier</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="37">
-      <c r="B4" s="43" t="inlineStr">
+    <row r="4" ht="16.5" customHeight="1" s="37">
+      <c r="A4" s="76" t="n"/>
+      <c r="B4" s="75" t="inlineStr">
         <is>
           <t>Network</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="37">
-      <c r="B5" s="43" t="inlineStr">
+    <row r="5" ht="16.5" customHeight="1" s="37">
+      <c r="A5" s="76" t="n"/>
+      <c r="B5" s="75" t="inlineStr">
         <is>
           <t>Maintenance terjadwal</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="37">
-      <c r="B6" s="43" t="inlineStr">
+    <row r="6" ht="30" customHeight="1" s="37">
+      <c r="A6" s="76" t="n"/>
+      <c r="B6" s="75" t="inlineStr">
         <is>
           <t>Pelanggan atau app-level</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="37">
-      <c r="B7" s="43" t="inlineStr">
+    <row r="7" ht="16.5" customHeight="1" s="37">
+      <c r="A7" s="76" t="n"/>
+      <c r="B7" s="75" t="inlineStr">
         <is>
           <t>Keamanan</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="37">
-      <c r="B8" s="43" t="inlineStr">
+    <row r="8" ht="16.5" customHeight="1" s="37">
+      <c r="A8" s="76" t="n"/>
+      <c r="B8" s="75" t="inlineStr">
         <is>
           <t>Lainnya</t>
         </is>
@@ -1273,7 +1430,7 @@
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1289,8 +1446,8 @@
     <col width="9" customWidth="1" style="36" min="1" max="1"/>
     <col width="22" customWidth="1" style="36" min="2" max="2"/>
     <col width="20" customWidth="1" style="36" min="3" max="3"/>
-    <col width="12" customWidth="1" style="36" min="4" max="4"/>
-    <col width="10" customWidth="1" style="36" min="5" max="5"/>
+    <col width="18" customWidth="1" style="36" min="4" max="4"/>
+    <col width="11" customWidth="1" style="36" min="5" max="5"/>
     <col width="36" customWidth="1" style="36" min="6" max="6"/>
     <col width="12" customWidth="1" style="36" min="7" max="7"/>
     <col width="20" customWidth="1" style="36" min="8" max="8"/>
@@ -1307,7 +1464,7 @@
     <row r="2" ht="15" customHeight="1" s="37">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Target availability dalam persen (0.999 = 99.9%). Kombinasi Pelanggan dan Layanan harus unik. Availability dihitung dari menit kalender penuh; Jam layanan dan Pengecualian kontrak tidak masuk rumus.</t>
+          <t>Target availability ditulis dalam persen (0.999 = 99.9%). Kombinasi Pelanggan dan Layanan harus unik. Availability dihitung dari menit kalender penuh; kolom Jam layanan dan Pengecualian kontrak tidak masuk rumus.</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1998,9 @@
     <col width="22" customWidth="1" style="36" min="2" max="2"/>
     <col width="20" customWidth="1" style="36" min="3" max="3"/>
     <col width="15" customWidth="1" style="36" min="4" max="5"/>
-    <col width="9" customWidth="1" style="36" min="6" max="7"/>
+    <col width="13" customWidth="1" style="37" min="5" max="5"/>
+    <col width="11" customWidth="1" style="36" min="6" max="7"/>
+    <col width="13" customWidth="1" style="37" min="7" max="7"/>
     <col width="20" customWidth="1" style="36" min="8" max="8"/>
     <col width="28" customWidth="1" style="36" min="9" max="9"/>
     <col width="14" customWidth="1" style="36" min="10" max="10"/>
@@ -1858,7 +2017,7 @@
     <row r="2" ht="15" customHeight="1" s="37">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>Durasi dihitung otomatis dalam menit. Pelanggan dan Layanan ditulis persis seperti di Parameter SLA; bila berbeda, downtime tidak terhitung di Laporan Bulanan. Downtime lintas bulan masuk seluruhnya ke bulan Mulai.</t>
+          <t>Durasi dihitung otomatis dalam menit. Tulis Pelanggan dan Layanan persis seperti di Parameter SLA; jika berbeda, downtime tidak terhitung di Laporan Bulanan. Downtime lintas bulan masuk seluruhnya ke bulan Mulai.</t>
         </is>
       </c>
     </row>
@@ -5178,19 +5337,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="36" min="1" max="1"/>
     <col width="20" customWidth="1" style="36" min="2" max="2"/>
-    <col width="9" customWidth="1" style="36" min="3" max="3"/>
+    <col width="10" customWidth="1" style="36" min="3" max="3"/>
     <col width="12" customWidth="1" style="36" min="4" max="5"/>
+    <col width="18" customWidth="1" style="37" min="5" max="5"/>
     <col width="11" customWidth="1" style="36" min="6" max="6"/>
     <col width="12" customWidth="1" style="36" min="7" max="8"/>
+    <col width="13" customWidth="1" style="37" min="8" max="8"/>
     <col width="9" customWidth="1" style="36" min="9" max="9"/>
     <col width="10" customWidth="1" style="36" min="10" max="11"/>
+    <col width="13" customWidth="1" style="37" min="11" max="11"/>
     <col width="34" customWidth="1" style="36" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -5233,7 +5395,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="35.05" customHeight="1" s="37">
+    <row r="7" ht="43.5" customHeight="1" s="37">
       <c r="A7" s="52" t="inlineStr">
         <is>
           <t>Pelanggan</t>
@@ -6935,21 +7097,55 @@
       </c>
       <c r="L47" s="65" t="n"/>
     </row>
-    <row r="49" ht="15" customHeight="1" s="37">
-      <c r="A49" s="58" t="inlineStr">
+    <row r="48" s="37">
+      <c r="A48" s="76" t="n"/>
+      <c r="B48" s="76" t="n"/>
+      <c r="C48" s="76" t="n"/>
+      <c r="D48" s="76" t="n"/>
+      <c r="E48" s="76" t="n"/>
+      <c r="F48" s="76" t="n"/>
+      <c r="G48" s="76" t="n"/>
+      <c r="H48" s="76" t="n"/>
+      <c r="I48" s="76" t="n"/>
+      <c r="J48" s="76" t="n"/>
+      <c r="K48" s="76" t="n"/>
+      <c r="L48" s="76" t="n"/>
+    </row>
+    <row r="49" ht="57" customHeight="1" s="37">
+      <c r="A49" s="77" t="inlineStr">
         <is>
           <t>Disusun (Service Delivery Manager)</t>
         </is>
       </c>
-      <c r="B49" s="67" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="37">
-      <c r="A50" s="58" t="inlineStr">
+      <c r="B49" s="78" t="n"/>
+      <c r="C49" s="76" t="n"/>
+      <c r="D49" s="76" t="n"/>
+      <c r="E49" s="76" t="n"/>
+      <c r="F49" s="76" t="n"/>
+      <c r="G49" s="76" t="n"/>
+      <c r="H49" s="76" t="n"/>
+      <c r="I49" s="76" t="n"/>
+      <c r="J49" s="76" t="n"/>
+      <c r="K49" s="76" t="n"/>
+      <c r="L49" s="76" t="n"/>
+    </row>
+    <row r="50" ht="30" customHeight="1" s="37">
+      <c r="A50" s="77" t="inlineStr">
         <is>
           <t>Diperiksa (Head of Operation)</t>
         </is>
       </c>
-      <c r="B50" s="67" t="n"/>
+      <c r="B50" s="78" t="n"/>
+      <c r="C50" s="76" t="n"/>
+      <c r="D50" s="76" t="n"/>
+      <c r="E50" s="76" t="n"/>
+      <c r="F50" s="76" t="n"/>
+      <c r="G50" s="76" t="n"/>
+      <c r="H50" s="76" t="n"/>
+      <c r="I50" s="76" t="n"/>
+      <c r="J50" s="76" t="n"/>
+      <c r="K50" s="76" t="n"/>
+      <c r="L50" s="76" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F8:F47">
@@ -6967,6 +7163,6 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>